--- a/Mappe1_TestVersioning_fromXML.xlsx
+++ b/Mappe1_TestVersioning_fromXML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUTTERPH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{D1DB5932-6901-4A63-8586-CE704C3A20FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847B97A8-9C77-48BF-9F95-FBCC6EC0DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,6 +449,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/Mappe1_TestVersioning_fromXML.xlsx
+++ b/Mappe1_TestVersioning_fromXML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUTTERPH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847B97A8-9C77-48BF-9F95-FBCC6EC0DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F434203-8482-4992-9B50-81B07A21C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -451,6 +451,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">

--- a/Mappe1_TestVersioning_fromXML.xlsx
+++ b/Mappe1_TestVersioning_fromXML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KUTTERPH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847B97A8-9C77-48BF-9F95-FBCC6EC0DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32CB8E-237C-4834-BC3F-99D270D90DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="35">
   <si>
     <t>C1</t>
   </si>
@@ -58,9 +58,6 @@
     <t>C7</t>
   </si>
   <si>
-    <t>C8</t>
-  </si>
-  <si>
     <t>C9</t>
   </si>
   <si>
@@ -137,6 +134,12 @@
   </si>
   <si>
     <t>asdf</t>
+  </si>
+  <si>
+    <t>v06xxx</t>
+  </si>
+  <si>
+    <t>C8xxx</t>
   </si>
 </sst>
 </file>
@@ -184,7 +187,11 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -208,12 +215,13 @@
     <tableColumn id="5" xr3:uid="{254B5F08-E598-4A05-A1AA-939EE7B3617A}" name="C5"/>
     <tableColumn id="6" xr3:uid="{74B48B74-0172-4EF3-B46B-484303526D5D}" name="C6"/>
     <tableColumn id="7" xr3:uid="{AEFD3515-159F-4B7E-8C89-4E19E992556B}" name="C7"/>
-    <tableColumn id="8" xr3:uid="{ECAFD2E5-9254-4129-BF57-674C9837BBAC}" name="C8"/>
+    <tableColumn id="8" xr3:uid="{ECAFD2E5-9254-4129-BF57-674C9837BBAC}" name="C8xxx"/>
     <tableColumn id="9" xr3:uid="{8FCA4D6E-2AFE-426C-B27C-797C27C8C6C1}" name="C9"/>
-    <tableColumn id="10" xr3:uid="{9D1950F6-01AB-4D8A-AC2A-1A304CCC78F4}" name="C10">
+    <tableColumn id="10" xr3:uid="{9D1950F6-01AB-4D8A-AC2A-1A304CCC78F4}" name="C10" dataDxfId="0">
       <calculatedColumnFormula>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</calculatedColumnFormula>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -451,6 +459,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -476,764 +485,786 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v01v01v01</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v01v01v01v01</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v02v02v02</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v02v02v02v02</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v03v03v03</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v03v03v03v03</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v04v04v04</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v04v04v04v04</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J6" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v05v05v05</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v05v05v05v05</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v06v06v06</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v06v06v06v06xxx</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v07v07v07</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v07v07v07v07</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v08v08v08</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v08v08v08v08</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v09v09v09</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v09v09v09v09</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v10v10v10</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v10v10v10v10</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v11v11v11</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v11v11v11v11</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v12v12v12</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v12v12v12v12</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v13v13v13</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v13v13v13v13</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J15" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v14v14v14</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v14v14v14v14</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J16" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v15v15v15</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v15v15v15v15</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J17" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v16v16v16</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v16v16v16v16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v17v17v17</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v17v17v17v17</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J19" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v18v18v18</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v18v18v18v18</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J20" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v19v19v19</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v19v19v19v19</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J21" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v20v20v20</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v20v20v20v20</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J22" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
-        <v>v21v21v21</v>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
+        <v>v21v21v21v21</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>32</v>
       </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
       <c r="J23" t="str">
         <f>Tabelle1[[#This Row],[C1]]&amp;
-  Tabelle1[[#This Row],[C2]]&amp;
-    Tabelle1[[#This Row],[C3]]</f>
+    Tabelle1[[#This Row],[C2]]&amp;
+    Tabelle1[[#This Row],[C3]]&amp;
+         Tabelle1[[#This Row],[C4]]</f>
         <v>sfdsdfasdf</v>
       </c>
     </row>
